--- a/Agenturen_Zielliste_EmployerBranding_Media_ERWEITERT.xlsx
+++ b/Agenturen_Zielliste_EmployerBranding_Media_ERWEITERT.xlsx
@@ -1610,8 +1610,16 @@
         </is>
       </c>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>m.reineke@jobware.de; info@jobware.de</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Matthias Reineke (Geschäftsführer); Dr. Wolfgang Achilles (Geschäftsführer)</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n">
         <v>3</v>
       </c>
@@ -1622,7 +1630,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -1651,8 +1659,16 @@
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>info@stellenanzeigen.de</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Dr. Peter Langbauer (Geschäftsführer); Manuel Sigl (Geschäftsführer)</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n">
         <v>3</v>
       </c>
@@ -1663,7 +1679,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -1692,8 +1708,16 @@
         </is>
       </c>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>presse@yourfirm.de</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Christina Nachbauer (Presse &amp; PR); Jonas Lehmann (Geschäftsführer / ehem. Vertriebsleiter)</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n">
         <v>3</v>
       </c>
@@ -1704,7 +1728,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -1733,8 +1757,16 @@
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>info@meap.de</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Christoph Falcone (Leitung Sales); Richard Piatkowski (Geschäftsführer)</t>
+        </is>
+      </c>
       <c r="I23" s="6" t="n">
         <v>3</v>
       </c>
@@ -1745,7 +1777,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -1774,8 +1806,16 @@
         </is>
       </c>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>info@hr-universal.de</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>n/a (keine benannte Person auf Team-/Kontaktseite; Standorte Köln/Berlin/München)</t>
+        </is>
+      </c>
       <c r="I24" s="5" t="n">
         <v>2</v>
       </c>
@@ -1786,7 +1826,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -1815,8 +1855,16 @@
         </is>
       </c>
       <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>mail@msw-partner.de</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Dipl.-Kfm. Christian Kramberg (verantwortlich/Geschäftsleitung, Ansprechpartner Bewerbung &amp; Karriere)</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="n">
         <v>3</v>
       </c>
@@ -1827,7 +1875,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -1856,8 +1904,16 @@
         </is>
       </c>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@vonq.com; hello@vonq.com</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Christophe Baudesson (Country Manager Deutschland) – persönl. Mail Muster christophe@vonq.com (Muster first@vonq.com – belegt via rocketreach/leadiq), vor Versand prüfen</t>
+        </is>
+      </c>
       <c r="I26" s="5" t="n">
         <v>2</v>
       </c>
@@ -1868,7 +1924,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -1897,8 +1953,16 @@
         </is>
       </c>
       <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>sales@gohiring.com; hello@gohiring.com</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Florian Behn (Geschäftsführer / Managing Director)</t>
+        </is>
+      </c>
       <c r="I27" s="6" t="n">
         <v>3</v>
       </c>
@@ -1909,7 +1973,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -1938,8 +2002,16 @@
         </is>
       </c>
       <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>info@persomatch.de</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Tristan Niewöhner (Geschäftsführer/CEO); Margarita Bobb (CMO/Marketing)</t>
+        </is>
+      </c>
       <c r="I28" s="6" t="n">
         <v>3</v>
       </c>
@@ -1950,7 +2022,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2112,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>zentrale@schulkurier.de</t>
+          <t>zentrale@schulkurier.de; willkommen@orange-yc.de</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn: Schulkurier / Orange YC + Vertrieb/New Business)</t>
+          <t>Björn Peters (Geschäftsführer Orange YC GmbH)</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2060,7 +2132,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum – Ansprechpartner via LinkedIn prüfen)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3102,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen (New Business via LinkedIn)</t>
+          <t>contact@elbkind.de</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Thorben Fasching (GF)</t>
+          <t>Thorben Fasching (Geschäftsführer)</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -3050,7 +3122,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3267,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen (Kontaktformular talentsconnect.com/kontakt)</t>
+          <t>presse@talentsconnect.com (allgemein: Kontaktformular talentsconnect.com/kontakt)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn: talentsconnect AG + New Business/Marketing)</t>
+          <t>n/a (kein benannter Sales/New-Business-Kontakt öffentlich; presse@ für Presse/Marketing)</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -3215,7 +3287,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum/Kontakt vor Versand prüfen</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -3360,12 +3432,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen (info über talention.de/kontakt)</t>
+          <t>info@talention.com</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Steffen Braun &amp; Christian Ternai (Geschäftsführer)</t>
+          <t>Leonardo Beadoy (Director Sales); GF: Steffen Braun &amp; Christian Ternai</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
@@ -3380,7 +3452,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum – via Firmenregister)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3487,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen (info über metahr.de)</t>
+          <t>info@metahr.de</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3435,7 +3507,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3542,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen (New Business via LinkedIn)</t>
+          <t>info@peakconcepts.de</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Melik Su &amp; Justin Wilkens (GF)</t>
+          <t>Melik Su (Gründer &amp; Geschäftsführer); Mit-GF Justin Wilkens</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
@@ -3490,7 +3562,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -4990,8 +5062,16 @@
         </is>
       </c>
       <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="n"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Kontaktformular universumglobal.com/de/about-us/contact/ (keine öffentliche E-Mail gefunden)</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>kein namentlicher Ansprechpartner öffentlich belegt</t>
+        </is>
+      </c>
       <c r="I84" s="5" t="n">
         <v>2</v>
       </c>
@@ -5002,7 +5082,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -5031,8 +5111,16 @@
         </is>
       </c>
       <c r="F85" s="2" t="n"/>
-      <c r="G85" s="2" t="n"/>
-      <c r="H85" s="2" t="n"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>info@trendence.com</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>kein namentlicher Ansprechpartner auf Kontaktseite (allg. info@; Support cs@trendence.com)</t>
+        </is>
+      </c>
       <c r="I85" s="5" t="n">
         <v>2</v>
       </c>
@@ -5043,7 +5131,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -5072,8 +5160,16 @@
         </is>
       </c>
       <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2" t="n"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>nb@elbdudler.de</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Fabiola Hedder (Geschäftsführung, zuständig New Business/Kundenanfragen)</t>
+        </is>
+      </c>
       <c r="I86" s="6" t="n">
         <v>3</v>
       </c>
@@ -5084,7 +5180,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -5113,8 +5209,16 @@
         </is>
       </c>
       <c r="F87" s="2" t="n"/>
-      <c r="G87" s="2" t="n"/>
-      <c r="H87" s="2" t="n"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>info@ministrygroup.de</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Ollmann &amp; David Cummins (Geschäftsführer)</t>
+        </is>
+      </c>
       <c r="I87" s="6" t="n">
         <v>3</v>
       </c>
@@ -5125,7 +5229,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5374,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>info@umspannwerx.de</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>Marcus Rudert (Geschäftsführer)</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -5290,7 +5394,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -5490,12 +5594,12 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>info@index-hr.de</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>Anselm Brinker (Senior Berater für Fachkräftegewinnung); GF: Jürgen Grenz</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -5510,7 +5614,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -5875,12 +5979,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>f.gehrmann@koenigsteiner.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>Florian Gehrmann (Sales Manager, Team Hamburg New Business)</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
@@ -5895,7 +5999,7 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -5985,12 +6089,12 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>info@sputnik-agentur.de</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>Klaus Baumann &amp; Maik Porsch (vertretungsberechtigte Gesellschafter)</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
@@ -6005,7 +6109,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6149,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn) - info@ als Notloesung</t>
+          <t>Frederic Bollhorst &amp; Jelena Mirkovic (Co-CEOs/Geschäftsführung)</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
@@ -6060,7 +6164,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6199,12 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>contact@jungmut.com</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>Tim Hufermann (Gründer &amp; Geschäftsführer)</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -6115,7 +6219,7 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6309,12 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>info@cyperfection.de</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>Marcus Birkmeir (Director Business Development / New Business); GF: Sven Korhummel, Georgios Manolidis, David Link</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -6225,7 +6329,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6419,12 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>kontakt@die-schätzefinder.de</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>David Rudolph (Inhaber / Geschäftsführer)</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -6335,7 +6439,7 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6584,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>info@achtung.de (Kreativ/PR-Unit Hamburg: native@achtung.de)</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6500,7 +6604,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6644,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Florian Liebold, Oliver Wonsyld-Drost (Vorstand) - Neubusiness via LinkedIn pruefen</t>
+          <t>Florian Liebold, Oliver Wonsyld-Drost (Vorstand)</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
@@ -6555,7 +6659,7 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -6590,12 +6694,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen</t>
+          <t>hallo@kolle-rebbe.de</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn: Accenture Song Germany + New Business)</t>
+          <t>kein dedizierter New-Business-Name öffentlich; Firmierung Accenture Song Brand Germany GmbH, HH</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr">
@@ -6610,7 +6714,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7187,8 +7291,16 @@
         </is>
       </c>
       <c r="F125" s="2" t="n"/>
-      <c r="G125" s="2" t="n"/>
-      <c r="H125" s="2" t="n"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>NB_Germany@wmglobal.com (New Business Germany); zentral contact.germany@wmglobal.com</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Dirk Fromm (President Wavemaker Germany, verantwortet Kunden-/Mediageschäft); Thorsten Ebbing (Chief Investment Officer WPP Media DACH – Media-Einkauf)</t>
+        </is>
+      </c>
       <c r="I125" s="5" t="n">
         <v>2</v>
       </c>
@@ -7199,7 +7311,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -7228,8 +7340,16 @@
         </is>
       </c>
       <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="n"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>michael.muelbuesch@mindshareworld.com (Muster vorname.nachname@mindshareworld.com, ~70% belegt)</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Michael Mülbüsch (Chief Investment Officer – Media-Einkauf/Investment); Katja Anette Brandt (CEO DACH / Vorsitzende Geschäftsführung)</t>
+        </is>
+      </c>
       <c r="I126" s="5" t="n">
         <v>2</v>
       </c>
@@ -7240,7 +7360,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7269,8 +7389,16 @@
         </is>
       </c>
       <c r="F127" s="2" t="n"/>
-      <c r="G127" s="2" t="n"/>
-      <c r="H127" s="2" t="n"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>jennifer.andree@zenithmedia.com (New Business); zentral office@zenithmedia.de</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Jennifer Andree (Managing Partner / CEO, New Business); Steven Mumendey (Managing Partner)</t>
+        </is>
+      </c>
       <c r="I127" s="5" t="n">
         <v>2</v>
       </c>
@@ -7281,7 +7409,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -7310,8 +7438,16 @@
         </is>
       </c>
       <c r="F128" s="2" t="n"/>
-      <c r="G128" s="2" t="n"/>
-      <c r="H128" s="2" t="n"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>business-development@publicismedia.com (New Business, zentral Publicis Media); alt birgit.konrad@publicismedia.com (Muster)</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Birgit Konrad (CEO Starcom Germany); Daniel Epailly (Chief Client Officer)</t>
+        </is>
+      </c>
       <c r="I128" s="6" t="n">
         <v>3</v>
       </c>
@@ -7322,7 +7458,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7351,8 +7487,16 @@
         </is>
       </c>
       <c r="F129" s="2" t="n"/>
-      <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2" t="n"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>business-development@publicismedia.com (New Business, zentral Publicis Media); alt simon.kramm@publicismedia.com (Muster)</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Simon Kramm (CEO Spark Foundry, seit 03/2026); Managing Partners Carolin Hedderich, Sahra Farsi, Ben Heuser</t>
+        </is>
+      </c>
       <c r="I129" s="6" t="n">
         <v>3</v>
       </c>
@@ -7363,7 +7507,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7392,8 +7536,16 @@
         </is>
       </c>
       <c r="F130" s="2" t="n"/>
-      <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2" t="n"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>judith.dohle@omnicommediagroup.com (New Business OMG, Muster first.last@omnicommediagroup.com)</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Tobias Lange (Managing Director PHD); Sabine Knöpfel-Ruth (CEO PHD); New Business OMG: Judith Dohle</t>
+        </is>
+      </c>
       <c r="I130" s="6" t="n">
         <v>3</v>
       </c>
@@ -7404,7 +7556,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7433,8 +7585,16 @@
         </is>
       </c>
       <c r="F131" s="2" t="n"/>
-      <c r="G131" s="2" t="n"/>
-      <c r="H131" s="2" t="n"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>kein zentrales Mail sichtbar – Notlösung: Kontakt via hearts-science.com/contact bzw. vorname.nachname@hearts-science.com (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Dominik Scholta (CEO / Managing Director Germany); Richard Kim &amp; Matthias Breitschaft (Managing Directors, Düsseldorf)</t>
+        </is>
+      </c>
       <c r="I131" s="6" t="n">
         <v>3</v>
       </c>
@@ -7445,7 +7605,7 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7474,8 +7634,16 @@
         </is>
       </c>
       <c r="F132" s="2" t="n"/>
-      <c r="G132" s="2" t="n"/>
-      <c r="H132" s="2" t="n"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>stefanie.tannrath@umww.com (belegt); zentral: info.de@umww.com</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Stefanie Tannrath (CEO UM Deutschland); René Kassner &amp; Sabrina Markhoff (Managing Partner)</t>
+        </is>
+      </c>
       <c r="I132" s="6" t="n">
         <v>3</v>
       </c>
@@ -7486,7 +7654,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -7515,8 +7683,16 @@
         </is>
       </c>
       <c r="F133" s="2" t="n"/>
-      <c r="G133" s="2" t="n"/>
-      <c r="H133" s="2" t="n"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>vorname.nachname@dentsu.com (Muster – belegt via Karin.Zimmermann@dentsu.com)</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Nina Brit Brando (CEO Carat Deutschland); Georg Berzbach (CEO Media dentsu DACH)</t>
+        </is>
+      </c>
       <c r="I133" s="5" t="n">
         <v>2</v>
       </c>
@@ -7527,7 +7703,7 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7556,8 +7732,16 @@
         </is>
       </c>
       <c r="F134" s="2" t="n"/>
-      <c r="G134" s="2" t="n"/>
-      <c r="H134" s="2" t="n"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>vorname.nachname@dentsu.com (Muster – belegt via Karin.Zimmermann@dentsu.com)</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Jan Kröger (Managing Director dentsu X Germany); Andrea Biebl (President dentsu X &amp; iProspect DE)</t>
+        </is>
+      </c>
       <c r="I134" s="6" t="n">
         <v>3</v>
       </c>
@@ -7568,7 +7752,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7597,8 +7781,16 @@
         </is>
       </c>
       <c r="F135" s="2" t="n"/>
-      <c r="G135" s="2" t="n"/>
-      <c r="H135" s="2" t="n"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>vorname.nachname@dentsu.com (Muster – belegt via Karin.Zimmermann@dentsu.com)</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Christoph Mauerer (Geschäftsführer/Managing Director iProspect Deutschland); Andrea Biebl (President)</t>
+        </is>
+      </c>
       <c r="I135" s="6" t="n">
         <v>3</v>
       </c>
@@ -7609,7 +7801,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7638,8 +7830,16 @@
         </is>
       </c>
       <c r="F136" s="2" t="n"/>
-      <c r="G136" s="2" t="n"/>
-      <c r="H136" s="2" t="n"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>info@jom-group.com</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Michael Jäschke (Geschäftsführer, inhaltlich verantwortlich); Nadja Vernimb, Roland Köster, Volker Neumann (weitere GF)</t>
+        </is>
+      </c>
       <c r="I136" s="4" t="n">
         <v>1</v>
       </c>
@@ -7650,7 +7850,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -7679,8 +7879,16 @@
         </is>
       </c>
       <c r="F137" s="2" t="n"/>
-      <c r="G137" s="2" t="n"/>
-      <c r="H137" s="2" t="n"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>welcome@moccamedia.com</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Cornelia Lamberty &amp; Patrick Becker (Geschäftsführung)</t>
+        </is>
+      </c>
       <c r="I137" s="4" t="n">
         <v>1</v>
       </c>
@@ -7691,7 +7899,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -7720,8 +7928,16 @@
         </is>
       </c>
       <c r="F138" s="2" t="n"/>
-      <c r="G138" s="2" t="n"/>
-      <c r="H138" s="2" t="n"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>info@planus-media.de</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Axel Wiehler (Geschäftsführer); Peter Herbrand (inhaltlich verantwortlich)</t>
+        </is>
+      </c>
       <c r="I138" s="4" t="n">
         <v>1</v>
       </c>
@@ -7732,7 +7948,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -7761,8 +7977,16 @@
         </is>
       </c>
       <c r="F139" s="2" t="n"/>
-      <c r="G139" s="2" t="n"/>
-      <c r="H139" s="2" t="n"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>info@mediateam360.de</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Aninka Vetter (Geschäftsführerin); Tobias Hoffmann &amp; Jessica Allgaier (ppa. General Manager)</t>
+        </is>
+      </c>
       <c r="I139" s="6" t="n">
         <v>3</v>
       </c>
@@ -7773,7 +7997,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -7802,8 +8026,16 @@
         </is>
       </c>
       <c r="F140" s="2" t="n"/>
-      <c r="G140" s="2" t="n"/>
-      <c r="H140" s="2" t="n"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>vorname.nachname@weischer.media (Muster – belegt via rocketreach.co Email-Format); zentral Tel. 040 809058-2000</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>GF-Ebene über Weischer-Gruppe (Jost von Brandis Serviceagentur GmbH, OOH-Spezialist Hamburg)</t>
+        </is>
+      </c>
       <c r="I140" s="5" t="n">
         <v>2</v>
       </c>
@@ -7814,7 +8046,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -7843,8 +8075,16 @@
         </is>
       </c>
       <c r="F141" s="2" t="n"/>
-      <c r="G141" s="2" t="n"/>
-      <c r="H141" s="2" t="n"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>info@crossvertise.com</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Maximilian Balbach &amp; Thomas Masek (Geschäftsführer); Joachim Wiebusch (Chief Revenue Officer)</t>
+        </is>
+      </c>
       <c r="I141" s="5" t="n">
         <v>2</v>
       </c>
@@ -7855,7 +8095,7 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -7895,7 +8135,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn: Boomerang Media Wien + GF/New Business)</t>
+          <t>Michel van Stralen (Geschäftsführer)</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
@@ -7910,7 +8150,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -7950,7 +8190,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Thomas Meyer (GF); New Business n/a (via LinkedIn)</t>
+          <t>Denise Evers (Head of Sales Marketing); alt. Claudia Nießen (Head of Media Purchasing); Thomas Meyer (GF)</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -7965,7 +8205,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -8000,12 +8240,12 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>info@ambermedia.de</t>
+          <t>anfrage@ambermedia.de</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Karsten Warrink (GF); Sales/New Business n/a (via LinkedIn)</t>
+          <t>Karsten Warrink (GF / Gruender)</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr">
@@ -8020,7 +8260,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8295,12 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>info@sit-watch.de</t>
+          <t>mediaberatung@sit-watch.de</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Harry Leyendecker (GF); Media/Sales n/a (via LinkedIn)</t>
+          <t>Harry Leyendecker (GF); Media-/Vertriebsteam ueber Mediaberatung</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -8075,7 +8315,7 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -8330,12 +8570,12 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen</t>
+          <t>kontakt-regional@stroeer.de</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Alexander Stotz, Dr. Andreas Müller-Leydig (Vertretungsberechtigte)</t>
+          <t>regionaler Vertrieb (Kontaktseite/Standortsuche); GF Alexander Stotz</t>
         </is>
       </c>
       <c r="I150" s="5" t="inlineStr">
@@ -8350,7 +8590,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -8550,12 +8790,12 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>officemanagement_muc@territory.group</t>
+          <t>contact@territory.group</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Marcus Hintzen, Oliver Reinke (GF); New Business n/a (via LinkedIn)</t>
+          <t>Constantin Röttger (Director Marketing &amp; New Business)</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
@@ -8570,7 +8810,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8900,12 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen</t>
+          <t>steffen.ruess@ruess-group.com</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Steffen Rueß (GF); Media-Kontakt n/a (via LinkedIn)</t>
+          <t>Steffen Rueß (GF)</t>
         </is>
       </c>
       <c r="I156" s="5" t="inlineStr">
@@ -8680,7 +8920,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -8830,7 +9070,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>GF: Minsoo Kee, Tai Hai Kim, Kyung Mo Lee, Daehoon Park; New Business n/a (via LinkedIn)</t>
+          <t>GF Minsoo Kee, Tai Hai Kim, Kyung Mo Lee, Daehoon Park</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
@@ -8845,7 +9085,7 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -8935,7 +9175,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>duesseldorf@blowup-media.de (prüfen)</t>
+          <t>duesseldorf@blowup-media.de</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8955,7 +9195,7 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -9045,12 +9285,12 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen (via LinkedIn)</t>
+          <t>michael.dunke@mbww.com (Gruppen-AP DACH) bzw. Muster vorname.nachname@mbww.com</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Jörg Philipp Heydenreich (GF); Media/New Business n/a (via LinkedIn)</t>
+          <t>Jörg Philipp Heydenreich (GF Kinesso, via LinkedIn); Michael Dunke (CEO IPG Mediabrands DACH)</t>
         </is>
       </c>
       <c r="I163" s="6" t="inlineStr">
@@ -9065,7 +9305,7 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9345,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>GF: Meike Specht, Julius Ewig, Jan Brockmann; Media n/a (via LinkedIn)</t>
+          <t>GF Meike Specht, Julius Ewig, Jan Brockmann; Standorte Berlin/Essen/Hamburg/Muenchen</t>
         </is>
       </c>
       <c r="I164" s="6" t="inlineStr">
@@ -9120,7 +9360,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -9210,12 +9450,12 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen (via LinkedIn)</t>
+          <t>michael.dunke@mbww.com</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Petra Gnauert, Michaela Mamczinski, Ilka Sauer (GF Holding); OOH-Einkauf n/a (via LinkedIn)</t>
+          <t>Michael Dunke (CEO IPG Mediabrands DACH)</t>
         </is>
       </c>
       <c r="I166" s="6" t="inlineStr">
@@ -9230,7 +9470,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -9475,8 +9715,16 @@
         </is>
       </c>
       <c r="F171" s="2" t="n"/>
-      <c r="G171" s="2" t="n"/>
-      <c r="H171" s="2" t="n"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>moin@edgar.de</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>n/a namentlich (nur Kontaktformular); GF Jan Risse. Produktion: produktion@edgar.de</t>
+        </is>
+      </c>
       <c r="I171" s="4" t="n">
         <v>1</v>
       </c>
@@ -9487,7 +9735,7 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -9516,8 +9764,16 @@
         </is>
       </c>
       <c r="F172" s="2" t="n"/>
-      <c r="G172" s="2" t="n"/>
-      <c r="H172" s="2" t="n"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>concept@einstieg.com</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Einstieg Concept (Marketing/Recruiting-Vertrieb), Tel 0221 39809-32; allgemein info@einstieg.com</t>
+        </is>
+      </c>
       <c r="I172" s="4" t="n">
         <v>1</v>
       </c>
@@ -9528,7 +9784,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -9557,8 +9813,16 @@
         </is>
       </c>
       <c r="F173" s="2" t="n"/>
-      <c r="G173" s="2" t="n"/>
-      <c r="H173" s="2" t="n"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>info@if-talent.de</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>n/a namentlich zentral (Ansprechpartner je Messe in Aussteller-Info-Boxen); Aussteller-Sprechstunde Do 9-11 Uhr, Tel Berlin +49 30 405771250</t>
+        </is>
+      </c>
       <c r="I173" s="5" t="n">
         <v>2</v>
       </c>
@@ -9569,7 +9833,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -9598,8 +9862,16 @@
         </is>
       </c>
       <c r="F174" s="2" t="n"/>
-      <c r="G174" s="2" t="n"/>
-      <c r="H174" s="2" t="n"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@stuzubi.de</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Vertriebsteam/Ansprechpartner im Verkauf (kein Einzelname), Tel +49 8131 90748-0</t>
+        </is>
+      </c>
       <c r="I174" s="5" t="n">
         <v>2</v>
       </c>
@@ -9610,7 +9882,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -9639,8 +9911,16 @@
         </is>
       </c>
       <c r="F175" s="2" t="n"/>
-      <c r="G175" s="2" t="n"/>
-      <c r="H175" s="2" t="n"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>hello@knowunity.com</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan Gresch (Sales/Brand Partnerships); Konstantin Paletta (Sales/Partnerships)</t>
+        </is>
+      </c>
       <c r="I175" s="5" t="n">
         <v>2</v>
       </c>
@@ -9651,7 +9931,7 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -9680,8 +9960,16 @@
         </is>
       </c>
       <c r="F176" s="2" t="n"/>
-      <c r="G176" s="2" t="n"/>
-      <c r="H176" s="2" t="n"/>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>support@simpleclub.com</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Powell (VP of Sales); Nicolai Schork &amp; Alexander Giesecke (Co-Founder &amp; CEOs)</t>
+        </is>
+      </c>
       <c r="I176" s="5" t="n">
         <v>2</v>
       </c>
@@ -9692,7 +9980,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -9837,12 +10125,12 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>info@deutsche-schuelerwerbung.de</t>
+          <t>info@hochschulwerbung.de</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>Athanasios Roussidis (Inhaber e.K.)</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
@@ -9857,7 +10145,7 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -10992,12 +11280,12 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>feedback@azubiyo.de</t>
+          <t>service@azubiyo.de</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn) – Marke der FUNKE Works GmbH</t>
+          <t>n/a (Marke der FUNKE Works GmbH; Arbeitgeber-/Werbekontakt via azubiyo.de/arbeitgeber)</t>
         </is>
       </c>
       <c r="I200" s="5" t="inlineStr">
@@ -11012,7 +11300,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -11707,12 +11995,12 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen</t>
+          <t>hello@appinio.com</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>Max Honig (CEO); Jonathan Kurfess (Gründer)</t>
+          <t>Jonathan Kurfess, Max Honig, Kai Granaß (Geschäftsführer)</t>
         </is>
       </c>
       <c r="I213" s="6" t="inlineStr">
@@ -11727,7 +12015,7 @@
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -11762,7 +12050,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen</t>
+          <t>info@youngmedia.de</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -11782,7 +12070,7 @@
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -11872,12 +12160,12 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>via Impressum prüfen</t>
+          <t>office@zoommedienfabrik.de</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>Felix Neunzerling (Geschäftsführer)</t>
+          <t>Felix Neunzerling (Gründer &amp; Geschäftsführer)</t>
         </is>
       </c>
       <c r="I216" s="6" t="inlineStr">
@@ -11892,7 +12180,7 @@
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 – Impressum vor Versand prüfen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -12196,8 +12484,16 @@
         </is>
       </c>
       <c r="F222" s="2" t="n"/>
-      <c r="G222" s="2" t="n"/>
-      <c r="H222" s="2" t="n"/>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>sales@studysmarter.de</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>GF Christian Felgenhauer, Maurice Khudhir, Simon Hohentanner, Till Söhlemann; B2B/Advertising via StudySmarter for Business</t>
+        </is>
+      </c>
       <c r="I222" s="6" t="n">
         <v>3</v>
       </c>
@@ -12208,7 +12504,7 @@
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -12237,8 +12533,16 @@
         </is>
       </c>
       <c r="F223" s="2" t="n"/>
-      <c r="G223" s="2" t="n"/>
-      <c r="H223" s="2" t="n"/>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>business@studydrive.net</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>Kampagnenmanager:in (persoenliche Betreuung, kein Name veroeffentlicht)</t>
+        </is>
+      </c>
       <c r="I223" s="4" t="n">
         <v>1</v>
       </c>
@@ -12249,7 +12553,7 @@
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -12278,8 +12582,16 @@
         </is>
       </c>
       <c r="F224" s="2" t="n"/>
-      <c r="G224" s="2" t="n"/>
-      <c r="H224" s="2" t="n"/>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>ruben.lampe@uninow.de</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>Ruben Lampe (Kooperationsmanager Erstkontakt); Alt: Romy Zimmermann (Unternehmensbereich) romy.zimmermann@uninow.de; Zentral: hello@uninow.de</t>
+        </is>
+      </c>
       <c r="I224" s="5" t="n">
         <v>2</v>
       </c>
@@ -12290,7 +12602,7 @@
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -12319,8 +12631,16 @@
         </is>
       </c>
       <c r="F225" s="2" t="n"/>
-      <c r="G225" s="2" t="n"/>
-      <c r="H225" s="2" t="n"/>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>vertrieb@e-fellows.net</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>Ralf Maywald (Vertriebsdirektor); GF: Michael Hies michael.hies@e-fellows.net; Muster: vorname.nachname@e-fellows.net</t>
+        </is>
+      </c>
       <c r="I225" s="5" t="n">
         <v>2</v>
       </c>
@@ -12331,7 +12651,7 @@
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -12360,8 +12680,16 @@
         </is>
       </c>
       <c r="F226" s="2" t="n"/>
-      <c r="G226" s="2" t="n"/>
-      <c r="H226" s="2" t="n"/>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>kontakt via Formular / Tel +49 221 912663-0</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>kein Name veroeffentlicht; belegtes Muster vorname.nachname@staufenbiel.de</t>
+        </is>
+      </c>
       <c r="I226" s="5" t="n">
         <v>2</v>
       </c>
@@ -12372,7 +12700,7 @@
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -12401,8 +12729,16 @@
         </is>
       </c>
       <c r="F227" s="2" t="n"/>
-      <c r="G227" s="2" t="n"/>
-      <c r="H227" s="2" t="n"/>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>hb@iqb.de</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>Helena Bilger (Sales Support); Alt: Andreas Saum asa@iqb.de; GF: Susanne Glueck sg@iqb.de; allg. info@iqb.de</t>
+        </is>
+      </c>
       <c r="I227" s="6" t="n">
         <v>3</v>
       </c>
@@ -12413,7 +12749,7 @@
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -12442,8 +12778,16 @@
         </is>
       </c>
       <c r="F228" s="2" t="n"/>
-      <c r="G228" s="2" t="n"/>
-      <c r="H228" s="2" t="n"/>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@jobvalley.com</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>kein Name veroeffentlicht; Firmenhotline 0800 2772000</t>
+        </is>
+      </c>
       <c r="I228" s="6" t="n">
         <v>3</v>
       </c>
@@ -12454,7 +12798,7 @@
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -12483,8 +12827,16 @@
         </is>
       </c>
       <c r="F229" s="2" t="n"/>
-      <c r="G229" s="2" t="n"/>
-      <c r="H229" s="2" t="n"/>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>info@workwise.io</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>kein Sales-Name veroeffentlicht (persoenl. Ansprechpartner nach Anfrage); alt support@workwise.io</t>
+        </is>
+      </c>
       <c r="I229" s="6" t="n">
         <v>3</v>
       </c>
@@ -12495,7 +12847,7 @@
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -12524,8 +12876,16 @@
         </is>
       </c>
       <c r="F230" s="2" t="n"/>
-      <c r="G230" s="2" t="n"/>
-      <c r="H230" s="2" t="n"/>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>service@zenjob.com</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>Vorstand: Friedrich von Trott (Vorsitz); Unternehmen/Sales via Kontaktseite + Tel 030 229 574 95</t>
+        </is>
+      </c>
       <c r="I230" s="6" t="n">
         <v>3</v>
       </c>
@@ -12536,7 +12896,7 @@
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -12565,8 +12925,16 @@
         </is>
       </c>
       <c r="F231" s="2" t="n"/>
-      <c r="G231" s="2" t="n"/>
-      <c r="H231" s="2" t="n"/>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@konaktiva.tu-darmstadt.de</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>GF/Orga: Alex Herchenroether, Lukas Besecke, Oemer Yagci; Ausweich: info@konaktiva-darmstadt.de</t>
+        </is>
+      </c>
       <c r="I231" s="6" t="n">
         <v>3</v>
       </c>
@@ -12577,7 +12945,7 @@
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -12606,8 +12974,16 @@
         </is>
       </c>
       <c r="F232" s="2" t="n"/>
-      <c r="G232" s="2" t="n"/>
-      <c r="H232" s="2" t="n"/>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>via bonding.de/kontakt (kein zentrales Bundesbuero-Postfach veroeffentlicht; lokale Gruppen: stadt@bonding.de, z.B. aachen@bonding.de)</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>kein Name veroeffentlicht; Kontakt ueber Hochschulgruppen/Formular</t>
+        </is>
+      </c>
       <c r="I232" s="6" t="n">
         <v>3</v>
       </c>
@@ -12618,7 +12994,7 @@
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>Tier 2/3 — noch nicht verifiziert (nur Name/Web/Relevanz)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -13258,12 +13634,12 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>info@iamstudent.com</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>Daniel Holzner (GF)</t>
+          <t>Sales: Damir Stambolija (Teamlead Sales); GF: Daniel Holzner (kein Direkt-Postfach veroeffentlicht)</t>
         </is>
       </c>
       <c r="I244" s="5" t="inlineStr">
@@ -13278,7 +13654,7 @@
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -13753,7 +14129,7 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen (Kontaktformular)</t>
+          <t>Kontaktformular squeaker.net/de/contact / Tel +49 221 986547-13 (corporate)</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -13773,7 +14149,7 @@
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14409,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn); Traeger: Praes. Prof. Dr. Niels Oberbeck</t>
+          <t>Web-Redaktion Hochschuljobboerse (kein Einzelname); Traeger vertreten durch Praes. Prof. Dr. Niels Oberbeck</t>
         </is>
       </c>
       <c r="I258" s="6" t="inlineStr">
@@ -14048,7 +14424,7 @@
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -14138,12 +14514,12 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen (webmaster@daad.de)</t>
+          <t>info@gate-germany.de</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>Dr. Kai Sicks (verantwortlich GATE-Germany)</t>
+          <t>Judith Lesch (Leiterin GATE-Germany-Buero &amp; Marketing, DAAD), lesch@daad.de</t>
         </is>
       </c>
       <c r="I260" s="6" t="inlineStr">
@@ -14158,7 +14534,7 @@
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -14193,12 +14569,12 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>contact@jobteaser.com</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>n/a namentlich; Publikationsverantwortlicher/CEO Adrien Ledoux (nicht Vertrieb). DE-Buero: Friesenplatz 4, 50672 Koeln</t>
         </is>
       </c>
       <c r="I261" s="6" t="inlineStr">
@@ -14213,7 +14589,7 @@
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>recherchiert 07/2026 – Kontakt belegt, E-Mail(-Muster) vor Versand kurz prüfen</t>
         </is>
       </c>
     </row>
@@ -14253,7 +14629,7 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>n/a (keine namentlichen Sales-/Werbekontakte oeffentlich; StudeerSnel B.V., Keizersgracht 424, Amsterdam)</t>
         </is>
       </c>
       <c r="I262" s="6" t="inlineStr">
@@ -14268,7 +14644,7 @@
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>verifiziert 07/2026 (Impressum)</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -14303,12 +14679,12 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>anfrage@barlagmessen.de</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>Michael Barlag (GF)</t>
+          <t>Justine Oetzel (Ansprechpartnerin Aussteller/Anfrage); GF Michael Barlag</t>
         </is>
       </c>
       <c r="I263" s="6" t="inlineStr">
@@ -14323,7 +14699,7 @@
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -14413,12 +14789,12 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>info@t5-interface.de</t>
+          <t>a.schambert@t5-karriereportal.de</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>n/a (via LinkedIn)</t>
+          <t>Andreas Schambert (Geschaeftsfuehrer T5 Interface GmbH); allgemein: info@t5-karriereportal.de</t>
         </is>
       </c>
       <c r="I265" s="6" t="inlineStr">
@@ -14433,7 +14809,7 @@
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -14468,12 +14844,12 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>info@studis-online.de</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>Oliver Iost (Herausgeber/Inhaber)</t>
+          <t>Oliver Iost (Herausgeber/Inhaber, zustaendig Werbung/Mediadaten), Tel +49 40 39806385</t>
         </is>
       </c>
       <c r="I266" s="6" t="inlineStr">
@@ -14488,7 +14864,7 @@
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -14523,12 +14899,12 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>via Impressum pruefen</t>
+          <t>kontakt@absolventa.de</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>Tobias Heberlein, Stephan Thurm (GF lt. Handelsregister)</t>
+          <t>n/a namentlich fuer Vertrieb; GF/CEO Christoph Jost (Greifswalder Str. 212, 10405 Berlin)</t>
         </is>
       </c>
       <c r="I267" s="6" t="inlineStr">
@@ -14543,7 +14919,7 @@
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
-          <t>recherchiert 07/2026 - Impressum vor Versand pruefen</t>
+          <t>verifiziert 07/2026 (Team-/Kontakt-/Impressumsseite)</t>
         </is>
       </c>
     </row>
@@ -14572,7 +14948,6 @@
           <t>Legende &amp; Hinweise</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">

--- a/Agenturen_Zielliste_EmployerBranding_Media_ERWEITERT.xlsx
+++ b/Agenturen_Zielliste_EmployerBranding_Media_ERWEITERT.xlsx
@@ -15302,9 +15302,9 @@
           <t>manuela.stockmaier@koenigsteiner.com</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
@@ -15317,7 +15317,11 @@
           <t>z.Hd. Manuela Stockmaier</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@koenigsteiner.com | Beleg: Impressum Königsteiner Agentur (stuttgart@koenigsteiner.com); rocketreach koenigsteiner.com häufigstes Muster {first}.{last}@koenigsteiner.com (40%). Alt allgemein: stuttgart@koenigsteiner.com</t>
@@ -17384,14 +17388,14 @@
           <t>alex.engel@essencemediacom.com</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -17399,7 +17403,11 @@
           <t>z.Hd. Alex Engel</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@essencemediacom.com | Beleg: presse@essencemediacom.com (Domain via Kontaktseite bestaetigt); Muster vorname.nachname laut RocketReach/Prospeo zu 99,8% belegt. Hinweis: 'Alex' evtl. Kurzform von Alexander.</t>
@@ -17455,9 +17463,9 @@
           <t>andrea.costales@essencemediacom.com</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
@@ -17470,7 +17478,11 @@
           <t>z.Hd. Andrea Costales</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@essencemediacom.com | Beleg: presse@essencemediacom.com (Domain bestaetigt); Muster vorname.nachname laut RocketReach 99,8%. Nachname evtl. 'Costales Garzon' (LinkedIn andreacostalesgarzon) - unsicher.</t>
@@ -17526,14 +17538,14 @@
           <t>karsten.reifer@essencemediacom.com</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -17541,7 +17553,11 @@
           <t>z.Hd. Karsten Reifer</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@essencemediacom.com | Beleg: presse@essencemediacom.com (Domain bestaetigt); Muster vorname.nachname laut RocketReach 99,8%.</t>
@@ -18027,14 +18043,14 @@
           <t>andreas.rommel@magnaglobal.com</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -18042,7 +18058,11 @@
           <t>z.Hd. Andreas Rommel</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@magnaglobal.com | Beleg: Muster vorname.nachname@magnaglobal.com laut RocketReach (96,1%). Alternativ IPG Mediabrands DE @mbww.com (first.last).</t>
@@ -19747,9 +19767,9 @@
           <t>karin.ross@publicismedia.de</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
         </is>
       </c>
       <c r="K68" s="14" t="inlineStr">
@@ -19762,7 +19782,11 @@
           <t>z.Hd. Karin Ross</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@publicismedia.de | Beleg: Impressum publicismedia.de (info@publicismedia.de, GF Karin Ross); rocketreach Publicis Media DE: {first}.{last}@publicismedia.de (69,9%). Hinweis: Impressum-Schreibung 'Roß' -&gt; Alt: karin.roß@</t>
@@ -21052,9 +21076,9 @@
           <t>xavier.reynaud@groupm.com</t>
         </is>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
         </is>
       </c>
       <c r="K87" s="14" t="inlineStr">
@@ -21067,7 +21091,11 @@
           <t>z.Hd. Xavier Reynaud</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@groupm.com | Beleg: GroupM-Standardmuster first.last@groupm.com (56,8% CH / 94% DE laut RocketReach/LeadIQ); kein einzelner oeffentlich benannter CH-Beleg gefunden -&gt; niedrige Sicherheit</t>
@@ -23383,14 +23411,14 @@
           <t>jens.dreger@essencemediacom.com</t>
         </is>
       </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J120" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K120" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -23398,7 +23426,11 @@
           <t>z.Hd. Jens Dreger</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@essencemediacom.com | Beleg: presse@essencemediacom.com (Domain bestaetigt); Muster vorname.nachname laut RocketReach 99,8%.</t>
@@ -23454,9 +23486,9 @@
           <t>linus.kuempel@groupm.com</t>
         </is>
       </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
+      <c r="J121" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
         </is>
       </c>
       <c r="K121" s="14" t="inlineStr">
@@ -23469,7 +23501,11 @@
           <t>z.Hd. Linus Kümpel</t>
         </is>
       </c>
-      <c r="M121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@groupm.com (ü -&gt; ue) | Beleg: GroupM Germany Muster {first}.{last}@groupm.com (leadiq/rocketreach ~94%). Hinweis: Umlaut ü als ue transliteriert; Alt: linus.kümpel@</t>
@@ -23525,9 +23561,9 @@
           <t>nils.rasmussen@groupm.com</t>
         </is>
       </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
+      <c r="J122" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
         </is>
       </c>
       <c r="K122" s="14" t="inlineStr">
@@ -23540,7 +23576,11 @@
           <t>z.Hd. Nils Rasmußen</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@groupm.com (ß -&gt; ss) | Beleg: GroupM Germany Muster {first}.{last}@groupm.com (leadiq/rocketreach ~94%). Hinweis: ß in Rasmußen als ss transliteriert</t>
@@ -23667,14 +23707,14 @@
           <t>andre.mettken@hearts-science.com</t>
         </is>
       </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J124" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K124" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -23682,7 +23722,11 @@
           <t>z.Hd. André Mettken</t>
         </is>
       </c>
-      <c r="M124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@hearts-science.com (é -&gt; e) | Beleg: Hearts &amp; Science Muster {first}.{last}@hearts-science.com (leadiq/prospeo 95%)</t>
@@ -23738,14 +23782,14 @@
           <t>clara.diehl@hearts-science.com</t>
         </is>
       </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J125" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K125" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -23753,7 +23797,11 @@
           <t>z.Hd. Clara Diehl</t>
         </is>
       </c>
-      <c r="M125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@hearts-science.com | Beleg: Hearts &amp; Science Muster {first}.{last}@hearts-science.com (leadiq/prospeo 95%)</t>
@@ -25537,14 +25585,14 @@
           <t>isabelle.wiedemann@publicismedia.de</t>
         </is>
       </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K150" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J150" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K150" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -25552,7 +25600,11 @@
           <t>z.Hd. Isabelle Wiedemann</t>
         </is>
       </c>
-      <c r="M150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@publicismedia.de | Beleg: Impressum publicismedia.de (info@publicismedia.de); rocketreach Publicis Media DE: {first}.{last}@publicismedia.de (69,9%)</t>
@@ -25604,14 +25656,14 @@
           <t>vanessa.lange@publicismedia.de</t>
         </is>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K151" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J151" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K151" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
@@ -25619,7 +25671,11 @@
           <t>z.Hd. Vanessa Lange</t>
         </is>
       </c>
-      <c r="M151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@publicismedia.de | Beleg: Impressum publicismedia.de (info@publicismedia.de); rocketreach Publicis Media DE: {first}.{last}@publicismedia.de (69,9%)</t>
@@ -26941,14 +26997,14 @@
           <t>frank.lattner@walldecaux.de</t>
         </is>
       </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K170" s="4" t="inlineStr">
-        <is>
-          <t>hoch</t>
+      <c r="J170" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K170" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -26958,7 +27014,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>[rolle_korrigieren] Sell-Side, kein Endkunden-Einkauf.</t>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren. | [rolle_korrigieren] Sell-Side, kein Endkunden-Einkauf.</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -27016,14 +27072,14 @@
           <t>mario.russo@walldecaux.de</t>
         </is>
       </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K171" s="4" t="inlineStr">
-        <is>
-          <t>hoch</t>
+      <c r="J171" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K171" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
@@ -27033,7 +27089,7 @@
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>[rolle_korrigieren] Sell-Side + Marketing-Rolle, kein Einkauf.</t>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren. | [rolle_korrigieren] Sell-Side + Marketing-Rolle, kein Einkauf.</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -27091,14 +27147,14 @@
           <t>martin.kleber@walldecaux.de</t>
         </is>
       </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K172" s="4" t="inlineStr">
-        <is>
-          <t>hoch</t>
+      <c r="J172" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K172" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -27108,7 +27164,7 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>[rolle_korrigieren] Sell-Side Medieneigentuemer.</t>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren. | [rolle_korrigieren] Sell-Side Medieneigentuemer.</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -27166,14 +27222,14 @@
           <t>volkmar.giehl@walldecaux.de</t>
         </is>
       </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K173" s="4" t="inlineStr">
-        <is>
-          <t>hoch</t>
+      <c r="J173" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K173" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
@@ -27183,7 +27239,7 @@
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>[rolle_korrigieren] Sell-Side Medieneigentuemer.</t>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren. | [rolle_korrigieren] Sell-Side Medieneigentuemer.</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
@@ -27608,14 +27664,14 @@
           <t>christina.vincenz@wppmedia.com</t>
         </is>
       </c>
-      <c r="J179" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K179" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J179" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K179" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L179" s="2" t="inlineStr">
@@ -27623,7 +27679,11 @@
           <t>z.Hd. Christina Vincenz</t>
         </is>
       </c>
-      <c r="M179" s="2" t="inlineStr"/>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N179" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@wppmedia.com | Beleg: WPP Media Rebrand 2025; Muster vorname.nachname@wppmedia.com laut RocketReach (99,8%). Domain via wppmedia.com/local/de bestaetigt.</t>
@@ -27679,14 +27739,14 @@
           <t>simon.chmiel@wppmedia.com</t>
         </is>
       </c>
-      <c r="J180" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
-        </is>
-      </c>
-      <c r="K180" s="5" t="inlineStr">
-        <is>
-          <t>mittel</t>
+      <c r="J180" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
+        </is>
+      </c>
+      <c r="K180" s="14" t="inlineStr">
+        <is>
+          <t>niedrig</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -27694,7 +27754,11 @@
           <t>z.Hd. Simon Chmiel</t>
         </is>
       </c>
-      <c r="M180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@wppmedia.com | Beleg: WPP Media Rebrand 2025; Muster vorname.nachname@wppmedia.com laut RocketReach (99,8%). Domain via wppmedia.com/local/de bestaetigt.</t>
@@ -29579,9 +29643,9 @@
           <t>andreas.germar@publicismedia.ch</t>
         </is>
       </c>
-      <c r="J208" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
+      <c r="J208" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
         </is>
       </c>
       <c r="K208" s="14" t="inlineStr">
@@ -29594,7 +29658,11 @@
           <t>z.Hd. Andreas Germar</t>
         </is>
       </c>
-      <c r="M208" s="2" t="inlineStr"/>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N208" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@publicismedia.ch | Beleg: Impressum publicismedia.ch (info@publicismedia.ch); Publicis-Gruppe durchgängig {first}.{last} (Publicis Media DE 69,9%). Domain bestätigt, Personen-Muster aus Konzernstandard abgeleitet</t>
@@ -29650,9 +29718,9 @@
           <t>jonas.hemmann@publicismedia.ch</t>
         </is>
       </c>
-      <c r="J209" s="3" t="inlineStr">
-        <is>
-          <t>rekonstruiert</t>
+      <c r="J209" s="8" t="inlineStr">
+        <is>
+          <t>rekonstruiert (Muster unbelegt)</t>
         </is>
       </c>
       <c r="K209" s="14" t="inlineStr">
@@ -29665,7 +29733,11 @@
           <t>z.Hd. Jonas Hemmann</t>
         </is>
       </c>
-      <c r="M209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
+        </is>
+      </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
           <t>vorname.nachname@publicismedia.ch | Beleg: Impressum publicismedia.ch (info@publicismedia.ch); Publicis-Gruppe durchgängig {first}.{last} (Publicis Media DE 69,9%). Domain bestätigt, Personen-Muster aus Konzernstandard abgeleitet</t>
@@ -30059,7 +30131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -30269,6 +30341,18 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Mail-Typ "rekonstruiert" vs. "(Muster unbelegt)"</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>"rekonstruiert" (114) = Firmen-Mailmuster durch mind. eine ECHTE Beispieladresse mit Klarnamen an der Domain belegt, Personen-Mail daraus gebildet. "rekonstruiert (Muster unbelegt)" (22) = Muster nur aus Aggregatoren (RocketReach/LeadIQ) oder nur Domain via Funktionsadresse bestaetigt, KEINE echte Einzeladresse gesehen -&gt; Sicherheit "niedrig", vor Versand per Mailtester/SMTP-Check verifizieren.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Agenturen_Zielliste_EmployerBranding_Media_ERWEITERT.xlsx
+++ b/Agenturen_Zielliste_EmployerBranding_Media_ERWEITERT.xlsx
@@ -15299,17 +15299,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>manuela.stockmaier@koenigsteiner.com</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>m.stockmaier@koenigsteiner.com</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -15317,14 +15317,10 @@
           <t>z.Hd. Manuela Stockmaier</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@koenigsteiner.com | Beleg: Impressum Königsteiner Agentur (stuttgart@koenigsteiner.com); rocketreach koenigsteiner.com häufigstes Muster {first}.{last}@koenigsteiner.com (40%). Alt allgemein: stuttgart@koenigsteiner.com</t>
+          <t>v.nachname@koenigsteiner.com | Beleg: s.wittbrodt@koenigsteiner.com (reale Adresse); weitere belegte Muster: t.palesch@, a.tasci@, m.heil@koenigsteiner.com</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -17385,12 +17381,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>alex.engel@essencemediacom.com</t>
-        </is>
-      </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
+          <t>alex.engel@wppmedia.com</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
@@ -17403,14 +17399,10 @@
           <t>z.Hd. Alex Engel</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@essencemediacom.com | Beleg: presse@essencemediacom.com (Domain via Kontaktseite bestaetigt); Muster vorname.nachname laut RocketReach/Prospeo zu 99,8% belegt. Hinweis: 'Alex' evtl. Kurzform von Alexander.</t>
+          <t>vorname.nachname@wppmedia.com (WPP-Media-Konzerndomain; EssenceMediacom migriert auf wppmedia.com) | Beleg: jennifer.leuchtenberg@wppmedia.com, axel.huebener@wppmedia.com (EssenceMediacom-Mitarbeiter auf essencemediacom.com/de/local/de)</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -17460,17 +17452,17 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>andrea.costales@essencemediacom.com</t>
-        </is>
-      </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K36" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>andrea.costales@wppmedia.com</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>mittel</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -17478,14 +17470,10 @@
           <t>z.Hd. Andrea Costales</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@essencemediacom.com | Beleg: presse@essencemediacom.com (Domain bestaetigt); Muster vorname.nachname laut RocketReach 99,8%. Nachname evtl. 'Costales Garzon' (LinkedIn andreacostalesgarzon) - unsicher.</t>
+          <t>vorname.nachname@wppmedia.com (WPP-Media-Konzerndomain; EssenceMediacom migriert auf wppmedia.com) | Beleg: jennifer.leuchtenberg@wppmedia.com, axel.huebener@wppmedia.com (EssenceMediacom-Mitarbeiter auf essencemediacom.com/de/local/de)</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -17535,17 +17523,17 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>karsten.reifer@essencemediacom.com</t>
-        </is>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K37" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>karsten.reifer@wppmedia.com</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>mittel</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -17553,14 +17541,10 @@
           <t>z.Hd. Karsten Reifer</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@essencemediacom.com | Beleg: presse@essencemediacom.com (Domain bestaetigt); Muster vorname.nachname laut RocketReach 99,8%.</t>
+          <t>vorname.nachname@wppmedia.com (WPP-Media-Konzerndomain; EssenceMediacom migriert auf wppmedia.com) | Beleg: jennifer.leuchtenberg@wppmedia.com, axel.huebener@wppmedia.com (EssenceMediacom-Mitarbeiter auf essencemediacom.com/de/local/de)</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -18040,17 +18024,17 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>andreas.rommel@magnaglobal.com</t>
-        </is>
-      </c>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K44" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>andreas.rommel@mbww.com</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>mittel</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -18058,14 +18042,10 @@
           <t>z.Hd. Andreas Rommel</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@magnaglobal.com | Beleg: Muster vorname.nachname@magnaglobal.com laut RocketReach (96,1%). Alternativ IPG Mediabrands DE @mbww.com (first.last).</t>
+          <t>vorname.nachname@mbww.com | Beleg: Echtes Klarnamen-Beispiel an Gruppendomain mbww.com aus offizieller IPG-Mediabrands/MAGNA-Pressemitteilung (Businesswire) verifiziert: rahel.rasu@mbww.com (Rahel Rasu, Chief Communications Officer, Mediabrands). Bestaetigt Muster vorname.nachname@mbww.com fuer IPG Mediabrands / MAGNA. mbww.com ist die belegte Gruppendomain (Magna Global Germany gehoert zu IPG Mediabrands).</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -19767,14 +19747,14 @@
           <t>karin.ross@publicismedia.de</t>
         </is>
       </c>
-      <c r="J68" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K68" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>mittel</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -19782,14 +19762,10 @@
           <t>z.Hd. Karin Ross</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@publicismedia.de | Beleg: Impressum publicismedia.de (info@publicismedia.de, GF Karin Ross); rocketreach Publicis Media DE: {first}.{last}@publicismedia.de (69,9%). Hinweis: Impressum-Schreibung 'Roß' -&gt; Alt: karin.roß@</t>
+          <t>vorname.nachname@publicismedia.de | Beleg: Reale Beispieladresse nicole.karepin@publicismedia.de (Nicole Karepin, Director Communications) im Pressekontakt-Block offizieller Publicis-Media-Pressemitteilungen (en.publicismedia.de).</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -21073,17 +21049,17 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>xavier.reynaud@groupm.com</t>
-        </is>
-      </c>
-      <c r="J87" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K87" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>info.ch@mindshareworld.com</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>funktional</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>mittel</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -21091,14 +21067,10 @@
           <t>z.Hd. Xavier Reynaud</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@groupm.com | Beleg: GroupM-Standardmuster first.last@groupm.com (56,8% CH / 94% DE laut RocketReach/LeadIQ); kein einzelner oeffentlich benannter CH-Beleg gefunden -&gt; niedrige Sicherheit</t>
+          <t>n/a (funktionale Mailbox der GroupM-Switzerland-Agentur am Standort Manessestrasse 85, Zürich) | Beleg: Keine reale Klarnamen-Beispieladresse fuer GroupM Switzerland gefunden (nur Aggregatoren behaupten first.last@groupm.com – kein zulaessiger Beweis). Rekonstruktion daher regelkonform NICHT durchgefuehrt. Verifizierte funktionale Mailbox stattdessen genutzt.</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -23408,17 +23380,17 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>jens.dreger@essencemediacom.com</t>
-        </is>
-      </c>
-      <c r="J120" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K120" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>jens.dreger@wppmedia.com</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>mittel</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -23426,14 +23398,10 @@
           <t>z.Hd. Jens Dreger</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M120" s="2" t="inlineStr"/>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@essencemediacom.com | Beleg: presse@essencemediacom.com (Domain bestaetigt); Muster vorname.nachname laut RocketReach 99,8%.</t>
+          <t>vorname.nachname@wppmedia.com (WPP-Media-Konzerndomain; EssenceMediacom migriert auf wppmedia.com) | Beleg: jennifer.leuchtenberg@wppmedia.com, axel.huebener@wppmedia.com (EssenceMediacom-Mitarbeiter auf essencemediacom.com/de/local/de)</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
@@ -23483,17 +23451,17 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>linus.kuempel@groupm.com</t>
-        </is>
-      </c>
-      <c r="J121" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K121" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>linus.kuempel@wppmedia.com</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
@@ -23501,14 +23469,10 @@
           <t>z.Hd. Linus Kümpel</t>
         </is>
       </c>
-      <c r="M121" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M121" s="2" t="inlineStr"/>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@groupm.com (ü -&gt; ue) | Beleg: GroupM Germany Muster {first}.{last}@groupm.com (leadiq/rocketreach ~94%). Hinweis: Umlaut ü als ue transliteriert; Alt: linus.kümpel@</t>
+          <t>vorname.nachname@wppmedia.com (ue statt ü) | Beleg: pia.tellefsen@wppmedia.com (Pia Tellefsen, WPP Media, belegt Domain+Muster) sowie juergen.blomenkamp@groupm.com (Juergen Blomenkamp, GroupM Germany – belegt ü→ue Transliteration und vorname.nachname-Muster)</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
@@ -23558,17 +23522,17 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>nils.rasmussen@groupm.com</t>
-        </is>
-      </c>
-      <c r="J122" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K122" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>nils.rasmussen@wppmedia.com</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>mittel</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -23576,14 +23540,10 @@
           <t>z.Hd. Nils Rasmußen</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M122" s="2" t="inlineStr"/>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@groupm.com (ß -&gt; ss) | Beleg: GroupM Germany Muster {first}.{last}@groupm.com (leadiq/rocketreach ~94%). Hinweis: ß in Rasmußen als ss transliteriert</t>
+          <t>vorname.nachname@wppmedia.com (ss statt ß, ue statt ü) | Beleg: pia.tellefsen@wppmedia.com (Pia Tellefsen, Nordic CFO, aktuelle WPP-Media-Leadership-Seite belegt Domain+Muster) sowie juergen.blomenkamp@groupm.com (Juergen Blomenkamp, GroupM Germany, Duesseldorf, PresseBox – belegt vorname.nachname-Muster der deutschen Org und ue-Transliteration fuer ü)</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
@@ -23704,17 +23664,17 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>andre.mettken@hearts-science.com</t>
-        </is>
-      </c>
-      <c r="J124" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K124" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>presse@omnicommediagroup.com</t>
+        </is>
+      </c>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>funktional</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>mittel</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -23722,14 +23682,10 @@
           <t>z.Hd. André Mettken</t>
         </is>
       </c>
-      <c r="M124" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M124" s="2" t="inlineStr"/>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@hearts-science.com (é -&gt; e) | Beleg: Hearts &amp; Science Muster {first}.{last}@hearts-science.com (leadiq/prospeo 95%)</t>
+          <t>kein belegtes Personen-Muster fuer hearts-science.com / omnicommediagroup.com gefunden | Beleg: Kein echtes Klarnamen-Beispiel an Firmendomain auffindbar. RocketReach zeigt nur maskiertes m***@resolutionmedia.com (Aggregator, kein Beweis). Impressum belegt nur Funktions-/Domain-Adresse presse(at)omnicommediagroup.com.</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
@@ -23779,17 +23735,17 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>clara.diehl@hearts-science.com</t>
-        </is>
-      </c>
-      <c r="J125" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K125" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>presse@omnicommediagroup.com</t>
+        </is>
+      </c>
+      <c r="J125" s="7" t="inlineStr">
+        <is>
+          <t>funktional</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>mittel</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -23797,14 +23753,10 @@
           <t>z.Hd. Clara Diehl</t>
         </is>
       </c>
-      <c r="M125" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M125" s="2" t="inlineStr"/>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@hearts-science.com | Beleg: Hearts &amp; Science Muster {first}.{last}@hearts-science.com (leadiq/prospeo 95%)</t>
+          <t>kein belegtes Personen-Muster fuer hearts-science.com / omnicommediagroup.com gefunden | Beleg: Kein echtes Klarnamen-Beispiel an Firmendomain auffindbar (Pressemitteilungen zum Wechsel von Pilot nennen keine persoenliche E-Mail). Impressum belegt nur Funktions-/Domain-Adresse presse(at)omnicommediagroup.com.</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
@@ -25585,14 +25537,14 @@
           <t>isabelle.wiedemann@publicismedia.de</t>
         </is>
       </c>
-      <c r="J150" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K150" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -25600,14 +25552,10 @@
           <t>z.Hd. Isabelle Wiedemann</t>
         </is>
       </c>
-      <c r="M150" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M150" s="2" t="inlineStr"/>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@publicismedia.de | Beleg: Impressum publicismedia.de (info@publicismedia.de); rocketreach Publicis Media DE: {first}.{last}@publicismedia.de (69,9%)</t>
+          <t>vorname.nachname@publicismedia.de | Beleg: Reale Beispieladresse nicole.karepin@publicismedia.de im Pressekontakt-Block offizieller Publicis-Media-Pressemitteilungen belegt DE-Muster vorname.nachname@publicismedia.de.</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
@@ -25656,14 +25604,14 @@
           <t>vanessa.lange@publicismedia.de</t>
         </is>
       </c>
-      <c r="J151" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K151" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
@@ -25671,14 +25619,10 @@
           <t>z.Hd. Vanessa Lange</t>
         </is>
       </c>
-      <c r="M151" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M151" s="2" t="inlineStr"/>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@publicismedia.de | Beleg: Impressum publicismedia.de (info@publicismedia.de); rocketreach Publicis Media DE: {first}.{last}@publicismedia.de (69,9%)</t>
+          <t>vorname.nachname@publicismedia.de | Beleg: Reale Beispieladresse nicole.karepin@publicismedia.de im Pressekontakt-Block offizieller Publicis-Media-Pressemitteilungen belegt DE-Muster vorname.nachname@publicismedia.de.</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -26997,14 +26941,14 @@
           <t>frank.lattner@walldecaux.de</t>
         </is>
       </c>
-      <c r="J170" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K170" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -27014,12 +26958,12 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren. | [rolle_korrigieren] Sell-Side, kein Endkunden-Einkauf.</t>
+          <t>[rolle_korrigieren] Sell-Side, kein Endkunden-Einkauf.</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@walldecaux.de | Beleg: frank.lattner@walldecaux.de</t>
+          <t>vorname.nachname@walldecaux.de | Beleg: frank.lattner@walldecaux.de (direkt gelistet als Sales Manager Verkaufsbüro Berlin/Dresden auf walldecaux.de/verkaufsbuero-berlin); weitere Belege: bernd.peschel@walldecaux.de, joachim.jebram@walldecaux.de, katrin.engelhardt@walldecaux.de</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
@@ -27072,14 +27016,14 @@
           <t>mario.russo@walldecaux.de</t>
         </is>
       </c>
-      <c r="J171" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K171" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
@@ -27089,12 +27033,12 @@
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren. | [rolle_korrigieren] Sell-Side + Marketing-Rolle, kein Einkauf.</t>
+          <t>[rolle_korrigieren] Sell-Side + Marketing-Rolle, kein Einkauf.</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@walldecaux.de | Beleg: bernd.peschel@walldecaux.de</t>
+          <t>vorname.nachname@walldecaux.de | Beleg: bernd.peschel@walldecaux.de, joachim.jebram@walldecaux.de, katrin.engelhardt@walldecaux.de, frank.lattner@walldecaux.de (reale Adressen auf walldecaux.de/verkaufsbuero-berlin)</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -27147,14 +27091,14 @@
           <t>martin.kleber@walldecaux.de</t>
         </is>
       </c>
-      <c r="J172" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K172" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -27164,12 +27108,12 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren. | [rolle_korrigieren] Sell-Side Medieneigentuemer.</t>
+          <t>[rolle_korrigieren] Sell-Side Medieneigentuemer.</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@walldecaux.de | Beleg: bernd.peschel@walldecaux.de</t>
+          <t>vorname.nachname@walldecaux.de | Beleg: bernd.peschel@walldecaux.de, joachim.jebram@walldecaux.de, katrin.engelhardt@walldecaux.de, frank.lattner@walldecaux.de (reale Adressen auf walldecaux.de/verkaufsbuero-berlin)</t>
         </is>
       </c>
       <c r="O172" s="2" t="inlineStr">
@@ -27222,14 +27166,14 @@
           <t>volkmar.giehl@walldecaux.de</t>
         </is>
       </c>
-      <c r="J173" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K173" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
@@ -27239,12 +27183,12 @@
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren. | [rolle_korrigieren] Sell-Side Medieneigentuemer.</t>
+          <t>[rolle_korrigieren] Sell-Side Medieneigentuemer.</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@walldecaux.de | Beleg: bernd.peschel@walldecaux.de</t>
+          <t>vorname.nachname@walldecaux.de | Beleg: bernd.peschel@walldecaux.de, joachim.jebram@walldecaux.de, katrin.engelhardt@walldecaux.de, frank.lattner@walldecaux.de (reale Adressen auf walldecaux.de/verkaufsbuero-berlin)</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
@@ -27664,14 +27608,14 @@
           <t>christina.vincenz@wppmedia.com</t>
         </is>
       </c>
-      <c r="J179" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K179" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L179" s="2" t="inlineStr">
@@ -27679,14 +27623,10 @@
           <t>z.Hd. Christina Vincenz</t>
         </is>
       </c>
-      <c r="M179" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M179" s="2" t="inlineStr"/>
       <c r="N179" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@wppmedia.com | Beleg: WPP Media Rebrand 2025; Muster vorname.nachname@wppmedia.com laut RocketReach (99,8%). Domain via wppmedia.com/local/de bestaetigt.</t>
+          <t>vorname.nachname@wppmedia.com | Beleg: pia.tellefsen@wppmedia.com (Pia Tellefsen, Nordic CFO, WPP Media – reale Klarnamen-Adresse belegt Domain und vorname.nachname-Muster) sowie juergen.blomenkamp@groupm.com (deutsche GroupM-Org, gleiches Muster)</t>
         </is>
       </c>
       <c r="O179" s="2" t="inlineStr">
@@ -27739,14 +27679,14 @@
           <t>simon.chmiel@wppmedia.com</t>
         </is>
       </c>
-      <c r="J180" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K180" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>rekonstruiert</t>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -27754,14 +27694,10 @@
           <t>z.Hd. Simon Chmiel</t>
         </is>
       </c>
-      <c r="M180" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M180" s="2" t="inlineStr"/>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@wppmedia.com | Beleg: WPP Media Rebrand 2025; Muster vorname.nachname@wppmedia.com laut RocketReach (99,8%). Domain via wppmedia.com/local/de bestaetigt.</t>
+          <t>vorname.nachname@wppmedia.com | Beleg: pia.tellefsen@wppmedia.com (Pia Tellefsen, Nordic CFO, WPP Media – reale Klarnamen-Adresse belegt Domain und vorname.nachname-Muster) sowie juergen.blomenkamp@groupm.com (deutsche GroupM-Org, gleiches Muster)</t>
         </is>
       </c>
       <c r="O180" s="2" t="inlineStr">
@@ -29640,17 +29576,17 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>andreas.germar@publicismedia.ch</t>
-        </is>
-      </c>
-      <c r="J208" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K208" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>info@publicismedia.ch</t>
+        </is>
+      </c>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>funktional</t>
+        </is>
+      </c>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L208" s="2" t="inlineStr">
@@ -29658,14 +29594,10 @@
           <t>z.Hd. Andreas Germar</t>
         </is>
       </c>
-      <c r="M208" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M208" s="2" t="inlineStr"/>
       <c r="N208" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@publicismedia.ch | Beleg: Impressum publicismedia.ch (info@publicismedia.ch); Publicis-Gruppe durchgängig {first}.{last} (Publicis Media DE 69,9%). Domain bestätigt, Personen-Muster aus Konzernstandard abgeleitet</t>
+          <t>kein reales Klarnamen-Beispiel an publicismedia.ch gefunden | Beleg: Keine echte Klarnamen-Beispieladresse fuer CH auffindbar (nur Aggregator RocketReach/FlashIntel = kein Beweis). Verifizierte funktionale Mailbox info@publicismedia.ch aus offiziellem Impressum.</t>
         </is>
       </c>
       <c r="O208" s="2" t="inlineStr">
@@ -29715,17 +29647,17 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>jonas.hemmann@publicismedia.ch</t>
-        </is>
-      </c>
-      <c r="J209" s="8" t="inlineStr">
-        <is>
-          <t>rekonstruiert (Muster unbelegt)</t>
-        </is>
-      </c>
-      <c r="K209" s="14" t="inlineStr">
-        <is>
-          <t>niedrig</t>
+          <t>info@publicismedia.ch</t>
+        </is>
+      </c>
+      <c r="J209" s="7" t="inlineStr">
+        <is>
+          <t>funktional</t>
+        </is>
+      </c>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>hoch</t>
         </is>
       </c>
       <c r="L209" s="2" t="inlineStr">
@@ -29733,14 +29665,10 @@
           <t>z.Hd. Jonas Hemmann</t>
         </is>
       </c>
-      <c r="M209" s="2" t="inlineStr">
-        <is>
-          <t>⚠ Muster nur aus Aggregator/Domain – keine echte Einzeladresse belegt; vor Versand verifizieren.</t>
-        </is>
-      </c>
+      <c r="M209" s="2" t="inlineStr"/>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>vorname.nachname@publicismedia.ch | Beleg: Impressum publicismedia.ch (info@publicismedia.ch); Publicis-Gruppe durchgängig {first}.{last} (Publicis Media DE 69,9%). Domain bestätigt, Personen-Muster aus Konzernstandard abgeleitet</t>
+          <t>kein reales Klarnamen-Beispiel an publicismedia.ch gefunden | Beleg: Keine echte Klarnamen-Beispieladresse fuer CH auffindbar (nur Aggregator RocketReach/FlashIntel = kein Beweis). Verifizierte funktionale Mailbox info@publicismedia.ch aus offiziellem Impressum.</t>
         </is>
       </c>
       <c r="O209" s="2" t="inlineStr">
@@ -30349,7 +30277,7 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>"rekonstruiert" (114) = Firmen-Mailmuster durch mind. eine ECHTE Beispieladresse mit Klarnamen an der Domain belegt, Personen-Mail daraus gebildet. "rekonstruiert (Muster unbelegt)" (22) = Muster nur aus Aggregatoren (RocketReach/LeadIQ) oder nur Domain via Funktionsadresse bestaetigt, KEINE echte Einzeladresse gesehen -&gt; Sicherheit "niedrig", vor Versand per Mailtester/SMTP-Check verifizieren.</t>
+          <t>"rekonstruiert" (131) = Firmen-Mailmuster durch mind. eine ECHTE Beispieladresse mit Klarnamen an der (aktiven) Firmendomain belegt, Personen-Mail exakt nach diesem Muster gebildet (Beleg je Zeile in Spalte "Muster/Beleg"). "funktional" (5) bzw. "allgemein" (69) = kein Personenmuster belegbar -&gt; verifizierte Funktions-/Sammelmail (media@/presse@/kontakt@/info@). "unbekannt" (3) = keine belastbare Adresse (leer statt geraten). Es wurde KEINE Personen-Mail ohne belegtes Muster gebildet.</t>
         </is>
       </c>
     </row>
